--- a/bousai_app/data/board_data.xlsx
+++ b/bousai_app/data/board_data.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,16 @@
           <t>状況</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>緯度</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>経度</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,6 +528,12 @@
           <t>確認中</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>40.8222</v>
+      </c>
+      <c r="F2" t="n">
+        <v>140.7474</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -540,6 +556,12 @@
           <t>対応中</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>40.8298</v>
+      </c>
+      <c r="F3" t="n">
+        <v>140.7346</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -562,6 +584,12 @@
           <t>現地確認中</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>40.7105</v>
+      </c>
+      <c r="F4" t="n">
+        <v>140.5908</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,6 +612,12 @@
           <t>通行止め</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>40.8898</v>
+      </c>
+      <c r="F5" t="n">
+        <v>140.8615</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -606,6 +640,12 @@
           <t>復旧作業中</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>40.6792</v>
+      </c>
+      <c r="F6" t="n">
+        <v>140.9318</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -627,6 +667,12 @@
         <is>
           <t>警戒中</t>
         </is>
+      </c>
+      <c r="E7" t="n">
+        <v>40.858</v>
+      </c>
+      <c r="F7" t="n">
+        <v>140.686</v>
       </c>
     </row>
   </sheetData>
